--- a/data/nzd0109/nzd0109.xlsx
+++ b/data/nzd0109/nzd0109.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S330"/>
+  <dimension ref="A1:S331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21211,13 +21211,13 @@
         <v>383.81</v>
       </c>
       <c r="H330" t="n">
-        <v>383.94</v>
+        <v>385.63</v>
       </c>
       <c r="I330" t="n">
         <v>390.97</v>
       </c>
       <c r="J330" t="n">
-        <v>384.73</v>
+        <v>386.74</v>
       </c>
       <c r="K330" t="n">
         <v>388.55</v>
@@ -21244,6 +21244,69 @@
         <v>364.23</v>
       </c>
       <c r="S330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>385.44</v>
+      </c>
+      <c r="C331" t="n">
+        <v>392.58</v>
+      </c>
+      <c r="D331" t="n">
+        <v>391.06</v>
+      </c>
+      <c r="E331" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="F331" t="n">
+        <v>389.4</v>
+      </c>
+      <c r="G331" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="H331" t="n">
+        <v>384.42</v>
+      </c>
+      <c r="I331" t="n">
+        <v>389.9</v>
+      </c>
+      <c r="J331" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="K331" t="n">
+        <v>388.81</v>
+      </c>
+      <c r="L331" t="n">
+        <v>399.97</v>
+      </c>
+      <c r="M331" t="n">
+        <v>403.36</v>
+      </c>
+      <c r="N331" t="n">
+        <v>408.98</v>
+      </c>
+      <c r="O331" t="n">
+        <v>403.08</v>
+      </c>
+      <c r="P331" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="R331" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="S331" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21260,7 +21323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25113,6 +25176,26 @@
       </c>
       <c r="B385" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -25281,28 +25364,28 @@
         <v>0.1305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1431654983948006</v>
+        <v>0.1394155318824445</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04512400597998267</v>
+        <v>0.04300056111090211</v>
       </c>
       <c r="M2" t="n">
-        <v>3.892474564318504</v>
+        <v>3.901600911342724</v>
       </c>
       <c r="N2" t="n">
-        <v>24.13534083426074</v>
+        <v>24.17121364231966</v>
       </c>
       <c r="O2" t="n">
-        <v>4.912773232529744</v>
+        <v>4.916422850235693</v>
       </c>
       <c r="P2" t="n">
-        <v>387.6209629650679</v>
+        <v>387.6604613353548</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25359,28 +25442,28 @@
         <v>0.1047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2764029024581089</v>
+        <v>0.2736403208974646</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1574632398679348</v>
+        <v>0.1554160602834235</v>
       </c>
       <c r="M3" t="n">
-        <v>3.715837444757653</v>
+        <v>3.721039448575667</v>
       </c>
       <c r="N3" t="n">
-        <v>22.74742511143613</v>
+        <v>22.73765548557341</v>
       </c>
       <c r="O3" t="n">
-        <v>4.769426077782957</v>
+        <v>4.768401774764099</v>
       </c>
       <c r="P3" t="n">
-        <v>389.5966579726113</v>
+        <v>389.6257562243079</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25437,28 +25520,28 @@
         <v>0.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2769208946872855</v>
+        <v>0.2717975067305031</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1173896329759349</v>
+        <v>0.1136595719499293</v>
       </c>
       <c r="M4" t="n">
-        <v>4.432703944503235</v>
+        <v>4.447334225056878</v>
       </c>
       <c r="N4" t="n">
-        <v>32.08397002208002</v>
+        <v>32.19022827537017</v>
       </c>
       <c r="O4" t="n">
-        <v>5.664271358443204</v>
+        <v>5.673643298214134</v>
       </c>
       <c r="P4" t="n">
-        <v>391.849252681375</v>
+        <v>391.903217289852</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25515,28 +25598,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2960838325480497</v>
+        <v>0.2913963810804778</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1152158901001203</v>
+        <v>0.1122641048193022</v>
       </c>
       <c r="M5" t="n">
-        <v>4.408894389800403</v>
+        <v>4.422189943525447</v>
       </c>
       <c r="N5" t="n">
-        <v>37.46206324012164</v>
+        <v>37.51886979599129</v>
       </c>
       <c r="O5" t="n">
-        <v>6.120626049688189</v>
+        <v>6.12526487557814</v>
       </c>
       <c r="P5" t="n">
-        <v>395.2741502900037</v>
+        <v>395.3235231825771</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25593,28 +25676,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2946505559386747</v>
+        <v>0.2924896254030929</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1399858379639491</v>
+        <v>0.1389343020513359</v>
       </c>
       <c r="M6" t="n">
-        <v>4.217187030401299</v>
+        <v>4.215353869258729</v>
       </c>
       <c r="N6" t="n">
-        <v>29.68064957572417</v>
+        <v>29.62690699792782</v>
       </c>
       <c r="O6" t="n">
-        <v>5.447995005111896</v>
+        <v>5.443060444081786</v>
       </c>
       <c r="P6" t="n">
-        <v>384.959570020494</v>
+        <v>384.9823310862736</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25671,28 +25754,28 @@
         <v>0.0857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3641907590333776</v>
+        <v>0.3598791103416614</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1734647041783922</v>
+        <v>0.1705113947490666</v>
       </c>
       <c r="M7" t="n">
-        <v>4.569594737490191</v>
+        <v>4.575225018975258</v>
       </c>
       <c r="N7" t="n">
-        <v>35.16782407015932</v>
+        <v>35.20536656312356</v>
       </c>
       <c r="O7" t="n">
-        <v>5.930246543792199</v>
+        <v>5.933411039454755</v>
       </c>
       <c r="P7" t="n">
-        <v>379.925184000182</v>
+        <v>379.9705985648218</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25749,28 +25832,28 @@
         <v>0.1168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3519537646276184</v>
+        <v>0.3490523533902395</v>
       </c>
       <c r="J8" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K8" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1529521519695144</v>
+        <v>0.1515381205289349</v>
       </c>
       <c r="M8" t="n">
-        <v>4.695452934316635</v>
+        <v>4.694922963242513</v>
       </c>
       <c r="N8" t="n">
-        <v>38.17340955775279</v>
+        <v>38.11800438552018</v>
       </c>
       <c r="O8" t="n">
-        <v>6.178463365413183</v>
+        <v>6.173978003323318</v>
       </c>
       <c r="P8" t="n">
-        <v>381.3052835363261</v>
+        <v>381.3358831677398</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25827,28 +25910,28 @@
         <v>0.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4010798942359858</v>
+        <v>0.3976993951502029</v>
       </c>
       <c r="J9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2190973432060023</v>
+        <v>0.2169615495577035</v>
       </c>
       <c r="M9" t="n">
-        <v>4.409741084179814</v>
+        <v>4.413388146347386</v>
       </c>
       <c r="N9" t="n">
-        <v>31.9050142394094</v>
+        <v>31.89692019944115</v>
       </c>
       <c r="O9" t="n">
-        <v>5.648452375598948</v>
+        <v>5.647735847172843</v>
       </c>
       <c r="P9" t="n">
-        <v>384.5593687373185</v>
+        <v>384.5949755098603</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25905,28 +25988,28 @@
         <v>0.101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3550332611358004</v>
+        <v>0.3532637550318403</v>
       </c>
       <c r="J10" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K10" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1333289426483788</v>
+        <v>0.1329615689163888</v>
       </c>
       <c r="M10" t="n">
-        <v>5.13296040599086</v>
+        <v>5.125221406222654</v>
       </c>
       <c r="N10" t="n">
-        <v>45.593749830712</v>
+        <v>45.4725129532038</v>
       </c>
       <c r="O10" t="n">
-        <v>6.752314405499199</v>
+        <v>6.743330998342273</v>
       </c>
       <c r="P10" t="n">
-        <v>380.6427932760456</v>
+        <v>380.661477904461</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25983,28 +26066,28 @@
         <v>0.163</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3021130138137141</v>
+        <v>0.3006954344597195</v>
       </c>
       <c r="J11" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K11" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1174289599511333</v>
+        <v>0.1171563077721625</v>
       </c>
       <c r="M11" t="n">
-        <v>4.559144494035927</v>
+        <v>4.553071669255598</v>
       </c>
       <c r="N11" t="n">
-        <v>38.17250803763586</v>
+        <v>38.07241160710727</v>
       </c>
       <c r="O11" t="n">
-        <v>6.178390408321237</v>
+        <v>6.170284564516233</v>
       </c>
       <c r="P11" t="n">
-        <v>382.9734608357995</v>
+        <v>382.9883921889331</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26061,28 +26144,28 @@
         <v>0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3800172540645162</v>
+        <v>0.3783121172437482</v>
       </c>
       <c r="J12" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K12" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1723283789804525</v>
+        <v>0.1719867000483404</v>
       </c>
       <c r="M12" t="n">
-        <v>4.813761455686603</v>
+        <v>4.809622001300333</v>
       </c>
       <c r="N12" t="n">
-        <v>38.59626351455375</v>
+        <v>38.5018439429187</v>
       </c>
       <c r="O12" t="n">
-        <v>6.212589115220299</v>
+        <v>6.20498541037114</v>
       </c>
       <c r="P12" t="n">
-        <v>392.5008358091598</v>
+        <v>392.5187960030214</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26139,28 +26222,28 @@
         <v>0.0619</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5265845713317698</v>
+        <v>0.5212835576150121</v>
       </c>
       <c r="J13" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K13" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2026737092527565</v>
+        <v>0.1999970340596896</v>
       </c>
       <c r="M13" t="n">
-        <v>6.373145412808097</v>
+        <v>6.376040150783758</v>
       </c>
       <c r="N13" t="n">
-        <v>60.7032997847335</v>
+        <v>60.73718668130216</v>
       </c>
       <c r="O13" t="n">
-        <v>7.791232237889813</v>
+        <v>7.793406615935175</v>
       </c>
       <c r="P13" t="n">
-        <v>397.727659127396</v>
+        <v>397.7834946667244</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26217,28 +26300,28 @@
         <v>0.1021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5451353062539047</v>
+        <v>0.5431475666950133</v>
       </c>
       <c r="J14" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K14" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2450771419203107</v>
+        <v>0.2449427394876647</v>
       </c>
       <c r="M14" t="n">
-        <v>5.674908250257888</v>
+        <v>5.667410807281058</v>
       </c>
       <c r="N14" t="n">
-        <v>50.93845397445335</v>
+        <v>50.81472391860406</v>
       </c>
       <c r="O14" t="n">
-        <v>7.137118044032434</v>
+        <v>7.128444705446207</v>
       </c>
       <c r="P14" t="n">
-        <v>397.5301466805753</v>
+        <v>397.5510835270437</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26295,28 +26378,28 @@
         <v>0.1046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5280075300440634</v>
+        <v>0.5245771098747877</v>
       </c>
       <c r="J15" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K15" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2021000001414686</v>
+        <v>0.200917898146908</v>
       </c>
       <c r="M15" t="n">
-        <v>5.748469203284238</v>
+        <v>5.748111180452756</v>
       </c>
       <c r="N15" t="n">
-        <v>61.24910594758612</v>
+        <v>61.15472615481664</v>
       </c>
       <c r="O15" t="n">
-        <v>7.826180802127314</v>
+        <v>7.820148729712027</v>
       </c>
       <c r="P15" t="n">
-        <v>394.4075820838111</v>
+        <v>394.4437146747662</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26373,28 +26456,28 @@
         <v>0.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2899238748021512</v>
+        <v>0.2918781694040097</v>
       </c>
       <c r="J16" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K16" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06402943685437801</v>
+        <v>0.06524977216939454</v>
       </c>
       <c r="M16" t="n">
-        <v>6.014648482391173</v>
+        <v>6.00406898921552</v>
       </c>
       <c r="N16" t="n">
-        <v>68.37350426107919</v>
+        <v>68.19591869008376</v>
       </c>
       <c r="O16" t="n">
-        <v>8.268827260324114</v>
+        <v>8.258082022484626</v>
       </c>
       <c r="P16" t="n">
-        <v>385.8166187501499</v>
+        <v>385.7960341791731</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26451,28 +26534,28 @@
         <v>0.0549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3960243181920419</v>
+        <v>0.3993169568349073</v>
       </c>
       <c r="J17" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K17" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1156324942531299</v>
+        <v>0.117951263800356</v>
       </c>
       <c r="M17" t="n">
-        <v>6.384346511392708</v>
+        <v>6.380912273626252</v>
       </c>
       <c r="N17" t="n">
-        <v>66.74734005595715</v>
+        <v>66.62911818992242</v>
       </c>
       <c r="O17" t="n">
-        <v>8.169904531630536</v>
+        <v>8.162666120203767</v>
       </c>
       <c r="P17" t="n">
-        <v>364.6193701205739</v>
+        <v>364.5846887814449</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26529,28 +26612,28 @@
         <v>0.1807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4223759007406479</v>
+        <v>-0.4182413512565898</v>
       </c>
       <c r="J18" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K18" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05720858842729437</v>
+        <v>0.05650663064625405</v>
       </c>
       <c r="M18" t="n">
-        <v>7.816966105948662</v>
+        <v>7.800133540379834</v>
       </c>
       <c r="N18" t="n">
-        <v>163.031543215991</v>
+        <v>162.6615931708368</v>
       </c>
       <c r="O18" t="n">
-        <v>12.76838060272292</v>
+        <v>12.75388541468194</v>
       </c>
       <c r="P18" t="n">
-        <v>365.3549632946575</v>
+        <v>365.3115380855194</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26588,7 +26671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S330"/>
+  <dimension ref="A1:S331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58530,7 +58613,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>-36.04604484995695,174.5360924165044</t>
+          <t>-36.046032842035416,174.5361039586211</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -58540,7 +58623,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>-36.04683446972675,174.5375424896183</t>
+          <t>-36.046818585661775,174.53755322061363</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -58584,6 +58667,103 @@
         </is>
       </c>
       <c r="S330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-36.04321050400146,174.53211584389032</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-36.0437044720474,174.53276949802517</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-36.044246437115234,174.53334814494974</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-36.04469262462487,174.5339837766537</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-36.045106213545395,174.53468970617666</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-36.04559667007641,174.53538188597975</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-36.046041439423135,174.5360956947391</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-36.04643999594588,174.53681786061722</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-36.04682957016452,174.53754579967702</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-36.047148627127996,174.53835678345655</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-36.04743682277224,174.53917129842912</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-36.04769336997666,174.53994024570065</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-36.04782118145503,174.54072736564234</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-36.04791538373604,174.54149445770076</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-36.04783878855173,174.54223322669586</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>-36.04757293712206,174.54301428325823</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>-36.04731816492043,174.54388884065307</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0109/nzd0109.xlsx
+++ b/data/nzd0109/nzd0109.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S331"/>
+  <dimension ref="A1:S332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21309,6 +21309,69 @@
       <c r="S331" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>387.18</v>
+      </c>
+      <c r="C332" t="n">
+        <v>395.19</v>
+      </c>
+      <c r="D332" t="n">
+        <v>392.97</v>
+      </c>
+      <c r="E332" t="n">
+        <v>400.32</v>
+      </c>
+      <c r="F332" t="n">
+        <v>390.38</v>
+      </c>
+      <c r="G332" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="H332" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="I332" t="n">
+        <v>392.93</v>
+      </c>
+      <c r="J332" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="K332" t="n">
+        <v>390</v>
+      </c>
+      <c r="L332" t="n">
+        <v>402.14</v>
+      </c>
+      <c r="M332" t="n">
+        <v>404.46</v>
+      </c>
+      <c r="N332" t="n">
+        <v>410.98</v>
+      </c>
+      <c r="O332" t="n">
+        <v>405.58</v>
+      </c>
+      <c r="P332" t="n">
+        <v>399.18</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="R332" t="n">
+        <v>362.02</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21323,7 +21386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B387"/>
+  <dimension ref="A1:B388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25196,6 +25259,16 @@
       </c>
       <c r="B387" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -25364,28 +25437,28 @@
         <v>0.1305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1394155318824445</v>
+        <v>0.136789025818744</v>
       </c>
       <c r="J2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04300056111090211</v>
+        <v>0.04165890986527077</v>
       </c>
       <c r="M2" t="n">
-        <v>3.901600911342724</v>
+        <v>3.904342919467036</v>
       </c>
       <c r="N2" t="n">
-        <v>24.17121364231966</v>
+        <v>24.15198587773465</v>
       </c>
       <c r="O2" t="n">
-        <v>4.916422850235693</v>
+        <v>4.914466998336102</v>
       </c>
       <c r="P2" t="n">
-        <v>387.6604613353548</v>
+        <v>387.6881991860632</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25442,28 +25515,28 @@
         <v>0.1047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2736403208974646</v>
+        <v>0.27252085790066</v>
       </c>
       <c r="J3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1554160602834235</v>
+        <v>0.1552244525455163</v>
       </c>
       <c r="M3" t="n">
-        <v>3.721039448575667</v>
+        <v>3.716415474564231</v>
       </c>
       <c r="N3" t="n">
-        <v>22.73765548557341</v>
+        <v>22.67873451007882</v>
       </c>
       <c r="O3" t="n">
-        <v>4.768401774764099</v>
+        <v>4.76221949410974</v>
       </c>
       <c r="P3" t="n">
-        <v>389.6257562243079</v>
+        <v>389.6375785832615</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25520,28 +25593,28 @@
         <v>0.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2717975067305031</v>
+        <v>0.2679260227757661</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1136595719499293</v>
+        <v>0.1111495620557856</v>
       </c>
       <c r="M4" t="n">
-        <v>4.447334225056878</v>
+        <v>4.454931922093519</v>
       </c>
       <c r="N4" t="n">
-        <v>32.19022827537017</v>
+        <v>32.20986123629828</v>
       </c>
       <c r="O4" t="n">
-        <v>5.673643298214134</v>
+        <v>5.675373224405447</v>
       </c>
       <c r="P4" t="n">
-        <v>391.903217289852</v>
+        <v>391.9441030298243</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25598,28 +25671,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2913963810804778</v>
+        <v>0.2896273289985345</v>
       </c>
       <c r="J5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1122641048193022</v>
+        <v>0.1117010818567776</v>
       </c>
       <c r="M5" t="n">
-        <v>4.422189943525447</v>
+        <v>4.418853408550164</v>
       </c>
       <c r="N5" t="n">
-        <v>37.51886979599129</v>
+        <v>37.4299249650242</v>
       </c>
       <c r="O5" t="n">
-        <v>6.12526487557814</v>
+        <v>6.118000078867619</v>
       </c>
       <c r="P5" t="n">
-        <v>395.3235231825771</v>
+        <v>395.3422056837227</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25676,28 +25749,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2924896254030929</v>
+        <v>0.2909516605512859</v>
       </c>
       <c r="J6" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K6" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1389343020513359</v>
+        <v>0.138456576868043</v>
       </c>
       <c r="M6" t="n">
-        <v>4.215353869258729</v>
+        <v>4.210338239183512</v>
       </c>
       <c r="N6" t="n">
-        <v>29.62690699792782</v>
+        <v>29.55584539740163</v>
       </c>
       <c r="O6" t="n">
-        <v>5.443060444081786</v>
+        <v>5.436528800383718</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9823310862736</v>
+        <v>384.9985731349952</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25754,28 +25827,28 @@
         <v>0.0857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3598791103416614</v>
+        <v>0.3576964413003537</v>
       </c>
       <c r="J7" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K7" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1705113947490666</v>
+        <v>0.1696566247882486</v>
       </c>
       <c r="M7" t="n">
-        <v>4.575225018975258</v>
+        <v>4.571166665721785</v>
       </c>
       <c r="N7" t="n">
-        <v>35.20536656312356</v>
+        <v>35.13615753060802</v>
       </c>
       <c r="O7" t="n">
-        <v>5.933411039454755</v>
+        <v>5.927576024869527</v>
       </c>
       <c r="P7" t="n">
-        <v>379.9705985648218</v>
+        <v>379.9936491676169</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25832,28 +25905,28 @@
         <v>0.1168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3490523533902395</v>
+        <v>0.3462737375278127</v>
       </c>
       <c r="J8" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K8" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1515381205289349</v>
+        <v>0.1502059984743399</v>
       </c>
       <c r="M8" t="n">
-        <v>4.694922963242513</v>
+        <v>4.694035030044025</v>
       </c>
       <c r="N8" t="n">
-        <v>38.11800438552018</v>
+        <v>38.06305287065432</v>
       </c>
       <c r="O8" t="n">
-        <v>6.173978003323318</v>
+        <v>6.169526146362807</v>
       </c>
       <c r="P8" t="n">
-        <v>381.3358831677398</v>
+        <v>381.3652274106612</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25910,28 +25983,28 @@
         <v>0.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3976993951502029</v>
+        <v>0.3962245236218109</v>
       </c>
       <c r="J9" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K9" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2169615495577035</v>
+        <v>0.2168265594204178</v>
       </c>
       <c r="M9" t="n">
-        <v>4.413388146347386</v>
+        <v>4.407427339917271</v>
       </c>
       <c r="N9" t="n">
-        <v>31.89692019944115</v>
+        <v>31.81751816940335</v>
       </c>
       <c r="O9" t="n">
-        <v>5.647735847172843</v>
+        <v>5.640701921694085</v>
       </c>
       <c r="P9" t="n">
-        <v>384.5949755098603</v>
+        <v>384.6105512463241</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25988,28 +26061,28 @@
         <v>0.101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3532637550318403</v>
+        <v>0.3515616864468898</v>
       </c>
       <c r="J10" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K10" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1329615689163888</v>
+        <v>0.1326174338732249</v>
       </c>
       <c r="M10" t="n">
-        <v>5.125221406222654</v>
+        <v>5.117229656392502</v>
       </c>
       <c r="N10" t="n">
-        <v>45.4725129532038</v>
+        <v>45.35772581611846</v>
       </c>
       <c r="O10" t="n">
-        <v>6.743330998342273</v>
+        <v>6.734814460407834</v>
       </c>
       <c r="P10" t="n">
-        <v>380.661477904461</v>
+        <v>380.6794530102325</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26066,28 +26139,28 @@
         <v>0.163</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3006954344597195</v>
+        <v>0.3000232222546864</v>
       </c>
       <c r="J11" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K11" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1171563077721625</v>
+        <v>0.1174255415805686</v>
       </c>
       <c r="M11" t="n">
-        <v>4.553071669255598</v>
+        <v>4.542957398149485</v>
       </c>
       <c r="N11" t="n">
-        <v>38.07241160710727</v>
+        <v>37.96091304136344</v>
       </c>
       <c r="O11" t="n">
-        <v>6.170284564516233</v>
+        <v>6.161242816296355</v>
       </c>
       <c r="P11" t="n">
-        <v>382.9883921889331</v>
+        <v>382.9954912480388</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26144,28 +26217,28 @@
         <v>0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3783121172437482</v>
+        <v>0.3779587098101306</v>
       </c>
       <c r="J12" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K12" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1719867000483404</v>
+        <v>0.1727391627387528</v>
       </c>
       <c r="M12" t="n">
-        <v>4.809622001300333</v>
+        <v>4.797239786738404</v>
       </c>
       <c r="N12" t="n">
-        <v>38.5018439429187</v>
+        <v>38.3864981593542</v>
       </c>
       <c r="O12" t="n">
-        <v>6.20498541037114</v>
+        <v>6.195683833069131</v>
       </c>
       <c r="P12" t="n">
-        <v>392.5187960030214</v>
+        <v>392.5225282474539</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26222,28 +26295,28 @@
         <v>0.0619</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5212835576150121</v>
+        <v>0.5167190969668122</v>
       </c>
       <c r="J13" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K13" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1999970340596896</v>
+        <v>0.1979093389239167</v>
       </c>
       <c r="M13" t="n">
-        <v>6.376040150783758</v>
+        <v>6.375917622431277</v>
       </c>
       <c r="N13" t="n">
-        <v>60.73718668130216</v>
+        <v>60.71616341749889</v>
       </c>
       <c r="O13" t="n">
-        <v>7.793406615935175</v>
+        <v>7.792057713948151</v>
       </c>
       <c r="P13" t="n">
-        <v>397.7834946667244</v>
+        <v>397.8316987541901</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26300,28 +26373,28 @@
         <v>0.1021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5431475666950133</v>
+        <v>0.542402151238455</v>
       </c>
       <c r="J14" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K14" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2449427394876647</v>
+        <v>0.2457457589110149</v>
       </c>
       <c r="M14" t="n">
-        <v>5.667410807281058</v>
+        <v>5.653976007523063</v>
       </c>
       <c r="N14" t="n">
-        <v>50.81472391860406</v>
+        <v>50.66553821245137</v>
       </c>
       <c r="O14" t="n">
-        <v>7.128444705446207</v>
+        <v>7.117972900513978</v>
       </c>
       <c r="P14" t="n">
-        <v>397.5510835270437</v>
+        <v>397.5589556667413</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26378,28 +26451,28 @@
         <v>0.1046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5245771098747877</v>
+        <v>0.522720892891995</v>
       </c>
       <c r="J15" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K15" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L15" t="n">
-        <v>0.200917898146908</v>
+        <v>0.2008599741288707</v>
       </c>
       <c r="M15" t="n">
-        <v>5.748111180452756</v>
+        <v>5.740052509197469</v>
       </c>
       <c r="N15" t="n">
-        <v>61.15472615481664</v>
+        <v>60.99683814582764</v>
       </c>
       <c r="O15" t="n">
-        <v>7.820148729712027</v>
+        <v>7.810047256312067</v>
       </c>
       <c r="P15" t="n">
-        <v>394.4437146747662</v>
+        <v>394.4633177018685</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26456,28 +26529,28 @@
         <v>0.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2918781694040097</v>
+        <v>0.2952977499628329</v>
       </c>
       <c r="J16" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K16" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06524977216939454</v>
+        <v>0.06704878411789217</v>
       </c>
       <c r="M16" t="n">
-        <v>6.00406898921552</v>
+        <v>5.999403200905768</v>
       </c>
       <c r="N16" t="n">
-        <v>68.19591869008376</v>
+        <v>68.08107874719211</v>
       </c>
       <c r="O16" t="n">
-        <v>8.258082022484626</v>
+        <v>8.251125907849916</v>
       </c>
       <c r="P16" t="n">
-        <v>385.7960341791731</v>
+        <v>385.7599208739968</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26534,28 +26607,28 @@
         <v>0.0549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3993169568349073</v>
+        <v>0.4045295775891068</v>
       </c>
       <c r="J17" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K17" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L17" t="n">
-        <v>0.117951263800356</v>
+        <v>0.1211002173523898</v>
       </c>
       <c r="M17" t="n">
-        <v>6.380912273626252</v>
+        <v>6.387218006896986</v>
       </c>
       <c r="N17" t="n">
-        <v>66.62911818992242</v>
+        <v>66.6397134401747</v>
       </c>
       <c r="O17" t="n">
-        <v>8.162666120203767</v>
+        <v>8.163315101120054</v>
       </c>
       <c r="P17" t="n">
-        <v>364.5846887814449</v>
+        <v>364.529639642866</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26612,28 +26685,28 @@
         <v>0.1807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4182413512565898</v>
+        <v>-0.4132058047488637</v>
       </c>
       <c r="J18" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K18" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05650663064625405</v>
+        <v>0.0555519801037706</v>
       </c>
       <c r="M18" t="n">
-        <v>7.800133540379834</v>
+        <v>7.785196035458207</v>
       </c>
       <c r="N18" t="n">
-        <v>162.6615931708368</v>
+        <v>162.3576898835246</v>
       </c>
       <c r="O18" t="n">
-        <v>12.75388541468194</v>
+        <v>12.74196569935442</v>
       </c>
       <c r="P18" t="n">
-        <v>365.3115380855194</v>
+        <v>365.258512343021</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26671,7 +26744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S331"/>
+  <dimension ref="A1:S332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58769,6 +58842,103 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-36.0431999311549,174.5321301081467</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-36.043688602389395,174.53279088285223</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-36.044234404040644,174.53336330616673</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-36.04465950752111,174.53401486515813</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-36.045098847883516,174.53469571049072</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-36.045572539190026,174.5354044219924</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-36.04602843676218,174.5361081930062</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-36.04641726981125,174.53683651289987</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-36.04681313292285,174.53755690438717</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-36.047139287471545,174.538363278974</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-36.04741950919098,174.53918250513655</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-36.0476840360454,174.5399443643483</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-36.047803373909446,174.5407308225</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-36.04789295155943,174.54149181859538</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-36.047818903013415,174.54222191914536</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>-36.04754928106592,174.54299396112333</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>-36.047306998459575,174.54387945329694</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0109/nzd0109.xlsx
+++ b/data/nzd0109/nzd0109.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S332"/>
+  <dimension ref="A1:S333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21370,6 +21370,69 @@
         <v>362.02</v>
       </c>
       <c r="S332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>388.22</v>
+      </c>
+      <c r="C333" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="D333" t="n">
+        <v>393.44</v>
+      </c>
+      <c r="E333" t="n">
+        <v>401</v>
+      </c>
+      <c r="F333" t="n">
+        <v>391.06</v>
+      </c>
+      <c r="G333" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="H333" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="I333" t="n">
+        <v>393.76</v>
+      </c>
+      <c r="J333" t="n">
+        <v>387.91</v>
+      </c>
+      <c r="K333" t="n">
+        <v>391.17</v>
+      </c>
+      <c r="L333" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="M333" t="n">
+        <v>405.19</v>
+      </c>
+      <c r="N333" t="n">
+        <v>410.72</v>
+      </c>
+      <c r="O333" t="n">
+        <v>405.94</v>
+      </c>
+      <c r="P333" t="n">
+        <v>399.28</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>382.86</v>
+      </c>
+      <c r="R333" t="n">
+        <v>363.03</v>
+      </c>
+      <c r="S333" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21386,7 +21449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B388"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25269,6 +25332,16 @@
       </c>
       <c r="B388" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-0.43</v>
       </c>
     </row>
   </sheetData>
@@ -25437,28 +25510,28 @@
         <v>0.1305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.136789025818744</v>
+        <v>0.1348319168016492</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04165890986527077</v>
+        <v>0.04075495184439926</v>
       </c>
       <c r="M2" t="n">
-        <v>3.904342919467036</v>
+        <v>3.903297446676596</v>
       </c>
       <c r="N2" t="n">
-        <v>24.15198587773465</v>
+        <v>24.10917449963888</v>
       </c>
       <c r="O2" t="n">
-        <v>4.914466998336102</v>
+        <v>4.910109418295979</v>
       </c>
       <c r="P2" t="n">
-        <v>387.6881991860632</v>
+        <v>387.7089398920307</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25515,28 +25588,28 @@
         <v>0.1047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.27252085790066</v>
+        <v>0.2713075601576336</v>
       </c>
       <c r="J3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1552244525455163</v>
+        <v>0.1549297101188637</v>
       </c>
       <c r="M3" t="n">
-        <v>3.716415474564231</v>
+        <v>3.712325223745476</v>
       </c>
       <c r="N3" t="n">
-        <v>22.67873451007882</v>
+        <v>22.62193021749776</v>
       </c>
       <c r="O3" t="n">
-        <v>4.76221949410974</v>
+        <v>4.756251698291183</v>
       </c>
       <c r="P3" t="n">
-        <v>389.6375785832615</v>
+        <v>389.6504366568381</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25593,28 +25666,28 @@
         <v>0.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2679260227757661</v>
+        <v>0.2643800247100295</v>
       </c>
       <c r="J4" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K4" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1111495620557856</v>
+        <v>0.1089442058414173</v>
       </c>
       <c r="M4" t="n">
-        <v>4.454931922093519</v>
+        <v>4.460590025807034</v>
       </c>
       <c r="N4" t="n">
-        <v>32.20986123629828</v>
+        <v>32.21111663445103</v>
       </c>
       <c r="O4" t="n">
-        <v>5.675373224405447</v>
+        <v>5.675483823820753</v>
       </c>
       <c r="P4" t="n">
-        <v>391.9441030298243</v>
+        <v>391.9816821848945</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25671,28 +25744,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2896273289985345</v>
+        <v>0.2882861046201341</v>
       </c>
       <c r="J5" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K5" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1117010818567776</v>
+        <v>0.1114555876369643</v>
       </c>
       <c r="M5" t="n">
-        <v>4.418853408550164</v>
+        <v>4.413061566901838</v>
       </c>
       <c r="N5" t="n">
-        <v>37.4299249650242</v>
+        <v>37.33124341829168</v>
       </c>
       <c r="O5" t="n">
-        <v>6.118000078867619</v>
+        <v>6.109929902895097</v>
       </c>
       <c r="P5" t="n">
-        <v>395.3422056837227</v>
+        <v>395.3564194757117</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25749,28 +25822,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2909516605512859</v>
+        <v>0.2898360847980048</v>
       </c>
       <c r="J6" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K6" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.138456576868043</v>
+        <v>0.1383576183107428</v>
       </c>
       <c r="M6" t="n">
-        <v>4.210338239183512</v>
+        <v>4.203236554926785</v>
       </c>
       <c r="N6" t="n">
-        <v>29.55584539740163</v>
+        <v>29.47654824426741</v>
       </c>
       <c r="O6" t="n">
-        <v>5.436528800383718</v>
+        <v>5.429230907252648</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9985731349952</v>
+        <v>385.010395587644</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25827,28 +25900,28 @@
         <v>0.0857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3576964413003537</v>
+        <v>0.3560766101169608</v>
       </c>
       <c r="J7" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K7" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1696566247882486</v>
+        <v>0.1693076263733077</v>
       </c>
       <c r="M7" t="n">
-        <v>4.571166665721785</v>
+        <v>4.564555929980886</v>
       </c>
       <c r="N7" t="n">
-        <v>35.13615753060802</v>
+        <v>35.05083248700051</v>
       </c>
       <c r="O7" t="n">
-        <v>5.927576024869527</v>
+        <v>5.920374353619922</v>
       </c>
       <c r="P7" t="n">
-        <v>379.9936491676169</v>
+        <v>380.0108155298371</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25905,28 +25978,28 @@
         <v>0.1168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3462737375278127</v>
+        <v>0.3440379379671981</v>
       </c>
       <c r="J8" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K8" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1502059984743399</v>
+        <v>0.1493399621018815</v>
       </c>
       <c r="M8" t="n">
-        <v>4.694035030044025</v>
+        <v>4.69070983198637</v>
       </c>
       <c r="N8" t="n">
-        <v>38.06305287065432</v>
+        <v>37.98747330195989</v>
       </c>
       <c r="O8" t="n">
-        <v>6.169526146362807</v>
+        <v>6.163397869840944</v>
       </c>
       <c r="P8" t="n">
-        <v>381.3652274106612</v>
+        <v>381.3889215742892</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25983,28 +26056,28 @@
         <v>0.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3962245236218109</v>
+        <v>0.3952632249229209</v>
       </c>
       <c r="J9" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K9" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2168265594204178</v>
+        <v>0.2171829621464765</v>
       </c>
       <c r="M9" t="n">
-        <v>4.407427339917271</v>
+        <v>4.398927609518704</v>
       </c>
       <c r="N9" t="n">
-        <v>31.81751816940335</v>
+        <v>31.72890454871988</v>
       </c>
       <c r="O9" t="n">
-        <v>5.640701921694085</v>
+        <v>5.632841605150981</v>
       </c>
       <c r="P9" t="n">
-        <v>384.6105512463241</v>
+        <v>384.6207387287211</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26061,28 +26134,28 @@
         <v>0.101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3515616864468898</v>
+        <v>0.3501559755453921</v>
       </c>
       <c r="J10" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K10" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1326174338732249</v>
+        <v>0.132482786236528</v>
       </c>
       <c r="M10" t="n">
-        <v>5.117229656392502</v>
+        <v>5.107933913179843</v>
       </c>
       <c r="N10" t="n">
-        <v>45.35772581611846</v>
+        <v>45.23654979341544</v>
       </c>
       <c r="O10" t="n">
-        <v>6.734814460407834</v>
+        <v>6.725812203252143</v>
       </c>
       <c r="P10" t="n">
-        <v>380.6794530102325</v>
+        <v>380.6943502061621</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26139,28 +26212,28 @@
         <v>0.163</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3000232222546864</v>
+        <v>0.3000609094326425</v>
       </c>
       <c r="J11" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K11" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1174255415805686</v>
+        <v>0.1181982036053975</v>
       </c>
       <c r="M11" t="n">
-        <v>4.542957398149485</v>
+        <v>4.52943554144111</v>
       </c>
       <c r="N11" t="n">
-        <v>37.96091304136344</v>
+        <v>37.84658404239629</v>
       </c>
       <c r="O11" t="n">
-        <v>6.161242816296355</v>
+        <v>6.151957740621785</v>
       </c>
       <c r="P11" t="n">
-        <v>382.9954912480388</v>
+        <v>382.995091853488</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26217,28 +26290,28 @@
         <v>0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3779587098101306</v>
+        <v>0.3776895424478102</v>
       </c>
       <c r="J12" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K12" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1727391627387528</v>
+        <v>0.1735614924128132</v>
       </c>
       <c r="M12" t="n">
-        <v>4.797239786738404</v>
+        <v>4.784411024903914</v>
       </c>
       <c r="N12" t="n">
-        <v>38.3864981593542</v>
+        <v>38.27144241917519</v>
       </c>
       <c r="O12" t="n">
-        <v>6.195683833069131</v>
+        <v>6.18639171239384</v>
       </c>
       <c r="P12" t="n">
-        <v>392.5225282474539</v>
+        <v>392.5253807820184</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26295,28 +26368,28 @@
         <v>0.0619</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5167190969668122</v>
+        <v>0.5126400104072864</v>
       </c>
       <c r="J13" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K13" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1979093389239167</v>
+        <v>0.1961983751078998</v>
       </c>
       <c r="M13" t="n">
-        <v>6.375917622431277</v>
+        <v>6.373620696165947</v>
       </c>
       <c r="N13" t="n">
-        <v>60.71616341749889</v>
+        <v>60.66332530528752</v>
       </c>
       <c r="O13" t="n">
-        <v>7.792057713948151</v>
+        <v>7.788666465145848</v>
       </c>
       <c r="P13" t="n">
-        <v>397.8316987541901</v>
+        <v>397.8749273808063</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26373,28 +26446,28 @@
         <v>0.1021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.542402151238455</v>
+        <v>0.5414778271791506</v>
       </c>
       <c r="J14" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K14" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2457457589110149</v>
+        <v>0.2464210819389765</v>
       </c>
       <c r="M14" t="n">
-        <v>5.653976007523063</v>
+        <v>5.641481263207859</v>
       </c>
       <c r="N14" t="n">
-        <v>50.66553821245137</v>
+        <v>50.51960854780033</v>
       </c>
       <c r="O14" t="n">
-        <v>7.117972900513978</v>
+        <v>7.107714720485082</v>
       </c>
       <c r="P14" t="n">
-        <v>397.5589556667413</v>
+        <v>397.5687513058013</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26451,28 +26524,28 @@
         <v>0.1046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.522720892891995</v>
+        <v>0.5210809273633388</v>
       </c>
       <c r="J15" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K15" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2008599741288707</v>
+        <v>0.2009487882771948</v>
       </c>
       <c r="M15" t="n">
-        <v>5.740052509197469</v>
+        <v>5.731003628210479</v>
       </c>
       <c r="N15" t="n">
-        <v>60.99683814582764</v>
+        <v>60.83413244825441</v>
       </c>
       <c r="O15" t="n">
-        <v>7.810047256312067</v>
+        <v>7.799623865819069</v>
       </c>
       <c r="P15" t="n">
-        <v>394.4633177018685</v>
+        <v>394.4806974403141</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26529,28 +26602,28 @@
         <v>0.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2952977499628329</v>
+        <v>0.2987164042699927</v>
       </c>
       <c r="J16" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K16" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06704878411789217</v>
+        <v>0.0688767546975122</v>
       </c>
       <c r="M16" t="n">
-        <v>5.999403200905768</v>
+        <v>5.994641867404488</v>
       </c>
       <c r="N16" t="n">
-        <v>68.08107874719211</v>
+        <v>67.96735669235046</v>
       </c>
       <c r="O16" t="n">
-        <v>8.251125907849916</v>
+        <v>8.24423172238326</v>
       </c>
       <c r="P16" t="n">
-        <v>385.7599208739968</v>
+        <v>385.7236912602298</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26607,28 +26680,28 @@
         <v>0.0549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4045295775891068</v>
+        <v>0.4090988734369591</v>
       </c>
       <c r="J17" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K17" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1211002173523898</v>
+        <v>0.1240246054572008</v>
       </c>
       <c r="M17" t="n">
-        <v>6.387218006896986</v>
+        <v>6.390423972906485</v>
       </c>
       <c r="N17" t="n">
-        <v>66.6397134401747</v>
+        <v>66.60216731057444</v>
       </c>
       <c r="O17" t="n">
-        <v>8.163315101120054</v>
+        <v>8.161015090696404</v>
       </c>
       <c r="P17" t="n">
-        <v>364.529639642866</v>
+        <v>364.4812159624113</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26685,28 +26758,28 @@
         <v>0.1807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4132058047488637</v>
+        <v>-0.4075815147165162</v>
       </c>
       <c r="J18" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K18" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0555519801037706</v>
+        <v>0.0544335686478471</v>
       </c>
       <c r="M18" t="n">
-        <v>7.785196035458207</v>
+        <v>7.77125145617955</v>
       </c>
       <c r="N18" t="n">
-        <v>162.3576898835246</v>
+        <v>162.1043923759592</v>
       </c>
       <c r="O18" t="n">
-        <v>12.74196569935442</v>
+        <v>12.7320223207454</v>
       </c>
       <c r="P18" t="n">
-        <v>365.258512343021</v>
+        <v>365.1990829841007</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26744,7 +26817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S332"/>
+  <dimension ref="A1:S333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58939,6 +59012,103 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-36.04319361175158,174.53213863390732</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-36.04368951443881,174.53278965383942</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-36.04423144302201,174.53336703693668</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-36.04465463314157,174.53401944095313</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-36.04509373701593,174.53469987674882</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-36.04556607555906,174.53541045842204</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-36.04602239727441,174.53611399821088</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-36.04641104449996,174.5368416222692</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-36.04680933971309,174.53755946701196</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-36.0471301047838,174.53836966532162</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-36.04741823261351,174.53918333143739</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-36.04767784170912,174.5399470976321</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-36.04780568889038,174.54073037310857</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-36.04788972132599,174.54149143856432</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-36.047818084678475,174.5422214538142</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>-36.0475559343321,174.54299967672253</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>-36.04729947970882,174.54387313247867</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
